--- a/data/trans_dic/P29A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,36; 64,65</t>
+          <t>57,0; 64,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,43; 61,05</t>
+          <t>53,27; 60,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,88; 64,37</t>
+          <t>56,8; 64,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47,91; 56,89</t>
+          <t>48,2; 57,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,44; 26,78</t>
+          <t>20,48; 26,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,54; 24,83</t>
+          <t>18,52; 25,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,25; 29,56</t>
+          <t>22,66; 29,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,93; 26,51</t>
+          <t>20,78; 26,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,65; 44,71</t>
+          <t>39,63; 44,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,41; 41,87</t>
+          <t>36,39; 41,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,51; 45,81</t>
+          <t>40,36; 45,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,04; 40,45</t>
+          <t>35,16; 40,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,23; 61,75</t>
+          <t>55,17; 61,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,94; 58,74</t>
+          <t>51,85; 58,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,77; 57,52</t>
+          <t>50,73; 57,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 51,56</t>
+          <t>18,88; 51,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,45; 29,02</t>
+          <t>23,26; 28,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,88; 27,51</t>
+          <t>21,79; 27,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,9; 31,76</t>
+          <t>25,82; 31,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 23,73</t>
+          <t>18,62; 23,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,76; 44,41</t>
+          <t>39,94; 44,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,5; 42,01</t>
+          <t>37,35; 42,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,8; 43,4</t>
+          <t>38,95; 43,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,46; 36,24</t>
+          <t>21,18; 36,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42,16; 49,9</t>
+          <t>41,72; 49,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,37; 59,76</t>
+          <t>52,15; 60,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,68; 57,97</t>
+          <t>50,98; 58,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42,3; 51,18</t>
+          <t>41,85; 50,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,19; 20,78</t>
+          <t>15,28; 20,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,12; 26,85</t>
+          <t>20,43; 26,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 31,39</t>
+          <t>24,78; 31,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 72,23</t>
+          <t>22,39; 67,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,99; 33,83</t>
+          <t>29,07; 34,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,52; 42,19</t>
+          <t>36,71; 42,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,36; 43,69</t>
+          <t>38,59; 43,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,77; 66,86</t>
+          <t>33,76; 62,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,47; 56,74</t>
+          <t>50,26; 56,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,0; 59,66</t>
+          <t>53,04; 60,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,73; 63,32</t>
+          <t>56,86; 63,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 51,59</t>
+          <t>43,79; 51,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 30,82</t>
+          <t>25,47; 30,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,21; 34,23</t>
+          <t>28,14; 33,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,51; 40,98</t>
+          <t>34,87; 41,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,71; 29,34</t>
+          <t>21,26; 29,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,05; 42,28</t>
+          <t>38,0; 42,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,71; 45,3</t>
+          <t>40,76; 45,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,89; 50,62</t>
+          <t>45,79; 50,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,86; 38,99</t>
+          <t>32,06; 38,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,24; 56,61</t>
+          <t>52,95; 56,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,36; 58,09</t>
+          <t>54,31; 58,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,41; 58,82</t>
+          <t>55,34; 58,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36,17; 49,79</t>
+          <t>34,76; 49,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 25,95</t>
+          <t>23,1; 26,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 27,35</t>
+          <t>24,29; 27,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,24; 32,44</t>
+          <t>29,13; 32,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,31; 40,2</t>
+          <t>23,29; 41,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,24; 40,67</t>
+          <t>38,25; 40,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,29; 41,71</t>
+          <t>39,16; 41,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,34; 44,85</t>
+          <t>42,4; 44,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,43; 42,68</t>
+          <t>33,1; 42,22</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas</t>
+          <t>Población que consumió bebidas alcohólicas en las últimas dos semanas (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>393631; 443647</t>
+          <t>391106; 440197</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>357570; 408530</t>
+          <t>356505; 407727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>365746; 413927</t>
+          <t>365243; 413843</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303361; 360260</t>
+          <t>305231; 361430</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>140276; 183809</t>
+          <t>140593; 184548</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>128141; 171625</t>
+          <t>127990; 172776</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155357; 197476</t>
+          <t>151389; 196636</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>141184; 178881</t>
+          <t>140191; 178184</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>544229; 613705</t>
+          <t>544019; 614982</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>495316; 569616</t>
+          <t>495051; 566165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>531199; 600672</t>
+          <t>529214; 598632</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>458327; 529039</t>
+          <t>459805; 528898</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>524132; 586073</t>
+          <t>523648; 585586</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506294; 572616</t>
+          <t>505494; 570501</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503255; 570152</t>
+          <t>502899; 564985</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>263859; 614494</t>
+          <t>225056; 616152</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>225266; 278791</t>
+          <t>223454; 277692</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>220319; 277019</t>
+          <t>219455; 276793</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>264875; 324861</t>
+          <t>264082; 324999</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>180423; 226954</t>
+          <t>178114; 225282</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>759294; 848103</t>
+          <t>762797; 854482</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>743148; 832629</t>
+          <t>740203; 832365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>781522; 874128</t>
+          <t>784488; 880048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>461103; 778568</t>
+          <t>454988; 786509</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>281049; 332628</t>
+          <t>278066; 330419</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>376149; 429222</t>
+          <t>374544; 431088</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>376273; 430358</t>
+          <t>378472; 431075</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>297067; 359436</t>
+          <t>293950; 356269</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103258; 141259</t>
+          <t>103873; 142157</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152242; 203127</t>
+          <t>154574; 203408</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>191537; 242125</t>
+          <t>191187; 243681</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>208501; 672492</t>
+          <t>208454; 627227</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>390290; 455444</t>
+          <t>391388; 459073</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>538577; 622236</t>
+          <t>541315; 623400</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>580720; 661406</t>
+          <t>584205; 664041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>551567; 1092162</t>
+          <t>551488; 1024127</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>469751; 528141</t>
+          <t>467812; 529586</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>483570; 544252</t>
+          <t>483927; 547822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>516787; 576746</t>
+          <t>517903; 573885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407436; 477578</t>
+          <t>405339; 474518</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>259897; 318518</t>
+          <t>263197; 317338</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>290984; 352991</t>
+          <t>290229; 349179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>353927; 420280</t>
+          <t>357643; 421418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>225737; 319803</t>
+          <t>231709; 325525</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>747335; 830574</t>
+          <t>746416; 828180</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>791241; 880568</t>
+          <t>792309; 883426</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>888630; 980301</t>
+          <t>886777; 975058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>642202; 786020</t>
+          <t>646212; 785210</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1721081; 1830050</t>
+          <t>1711533; 1832417</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1779918; 1902363</t>
+          <t>1778373; 1900727</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1821769; 1933711</t>
+          <t>1819409; 1934282</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1248887; 1719386</t>
+          <t>1200308; 1723251</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>774438; 871859</t>
+          <t>776264; 875351</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>846381; 953364</t>
+          <t>846842; 949519</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1019800; 1131476</t>
+          <t>1016079; 1129875</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>851493; 1468125</t>
+          <t>850746; 1518369</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2521204; 2681089</t>
+          <t>2521776; 2683702</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2656385; 2820098</t>
+          <t>2647611; 2819507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2868467; 3039082</t>
+          <t>2873027; 3037583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2375497; 3032422</t>
+          <t>2351846; 3000156</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P29A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P29A_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>57,0; 64,15</t>
+          <t>56,57; 64,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,27; 60,93</t>
+          <t>53,27; 61,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,8; 64,36</t>
+          <t>56,87; 64,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48,2; 57,08</t>
+          <t>46,82; 55,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,48; 26,89</t>
+          <t>20,62; 26,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,52; 25,0</t>
+          <t>18,52; 24,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,66; 29,43</t>
+          <t>23,15; 29,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,78; 26,41</t>
+          <t>21,22; 26,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 44,8</t>
+          <t>39,52; 44,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 41,62</t>
+          <t>36,07; 41,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40,36; 45,66</t>
+          <t>40,2; 45,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>35,16; 40,44</t>
+          <t>34,33; 39,54</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,17; 61,7</t>
+          <t>55,2; 61,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,85; 58,52</t>
+          <t>52,09; 58,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,73; 57,0</t>
+          <t>51,12; 57,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 51,7</t>
+          <t>44,6; 51,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,26; 28,9</t>
+          <t>23,15; 28,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,79; 27,48</t>
+          <t>21,56; 27,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,82; 31,78</t>
+          <t>26,12; 31,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,62; 23,55</t>
+          <t>18,76; 23,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,94; 44,74</t>
+          <t>39,95; 44,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,35; 42,0</t>
+          <t>37,27; 41,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38,95; 43,7</t>
+          <t>39,06; 43,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,18; 36,61</t>
+          <t>32,17; 36,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,72; 49,57</t>
+          <t>41,53; 49,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,15; 60,02</t>
+          <t>52,03; 59,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50,98; 58,07</t>
+          <t>50,9; 58,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41,85; 50,73</t>
+          <t>41,19; 49,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,28; 20,92</t>
+          <t>15,27; 21,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 26,89</t>
+          <t>20,62; 27,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,78; 31,59</t>
+          <t>24,93; 31,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 67,37</t>
+          <t>22,28; 27,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,07; 34,1</t>
+          <t>29,23; 34,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,71; 42,27</t>
+          <t>36,82; 42,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>38,59; 43,86</t>
+          <t>38,57; 43,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,76; 62,7</t>
+          <t>32,54; 37,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>50,26; 56,9</t>
+          <t>50,86; 57,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53,04; 60,05</t>
+          <t>52,76; 59,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,86; 63,0</t>
+          <t>56,71; 63,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43,79; 51,26</t>
+          <t>43,42; 50,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,47; 30,71</t>
+          <t>25,12; 30,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,14; 33,86</t>
+          <t>28,23; 33,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,87; 41,09</t>
+          <t>34,58; 40,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 29,86</t>
+          <t>25,51; 30,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,0; 42,16</t>
+          <t>37,76; 42,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,76; 45,45</t>
+          <t>40,61; 45,19</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,79; 50,35</t>
+          <t>46,01; 50,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32,06; 38,95</t>
+          <t>34,71; 38,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,95; 56,69</t>
+          <t>53,22; 56,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,31; 58,04</t>
+          <t>54,21; 57,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55,34; 58,84</t>
+          <t>55,33; 58,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,76; 49,91</t>
+          <t>45,81; 49,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 26,05</t>
+          <t>22,97; 25,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,29; 27,24</t>
+          <t>24,27; 27,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,13; 32,39</t>
+          <t>29,16; 32,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>23,29; 41,57</t>
+          <t>23,07; 25,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,25; 40,71</t>
+          <t>38,1; 40,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,16; 41,7</t>
+          <t>39,14; 41,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42,4; 44,83</t>
+          <t>42,29; 44,75</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,1; 42,22</t>
+          <t>34,4; 36,83</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>333157</t>
+          <t>353514</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>159637</t>
+          <t>172651</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>492794</t>
+          <t>526165</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>391106; 440197</t>
+          <t>388173; 443390</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>356505; 407727</t>
+          <t>356503; 408306</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>365243; 413843</t>
+          <t>365683; 412926</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305231; 361430</t>
+          <t>322362; 381310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>140593; 184548</t>
+          <t>141561; 183754</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>127990; 172776</t>
+          <t>127969; 171190</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>151389; 196636</t>
+          <t>154662; 198875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>140191; 178184</t>
+          <t>155344; 194168</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>544019; 614982</t>
+          <t>542505; 615453</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>495051; 566165</t>
+          <t>490705; 566379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>529214; 598632</t>
+          <t>527109; 598819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>459805; 528898</t>
+          <t>487700; 561588</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>476919</t>
+          <t>501905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>201444</t>
+          <t>223193</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>678363</t>
+          <t>725098</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>523648; 585586</t>
+          <t>523841; 586630</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>505494; 570501</t>
+          <t>507777; 572534</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>502899; 564985</t>
+          <t>506760; 570040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225056; 616152</t>
+          <t>467336; 539831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>223454; 277692</t>
+          <t>222394; 278502</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>219455; 276793</t>
+          <t>217129; 277211</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>264082; 324999</t>
+          <t>267119; 324507</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178114; 225282</t>
+          <t>200456; 250048</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>762797; 854482</t>
+          <t>762898; 848919</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>740203; 832365</t>
+          <t>738763; 830133</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>784488; 880048</t>
+          <t>786588; 873585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>454988; 786509</t>
+          <t>680883; 769692</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>326527</t>
+          <t>361328</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>376097</t>
+          <t>201134</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>702624</t>
+          <t>562462</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>278066; 330419</t>
+          <t>276805; 329445</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>374544; 431088</t>
+          <t>373659; 430243</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>378472; 431075</t>
+          <t>377857; 437388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>293950; 356269</t>
+          <t>329331; 393152</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>103873; 142157</t>
+          <t>103774; 143665</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>154574; 203408</t>
+          <t>156013; 206182</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>191187; 243681</t>
+          <t>192336; 242467</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>208454; 627227</t>
+          <t>180355; 224923</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>391388; 459073</t>
+          <t>393546; 460473</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541315; 623400</t>
+          <t>542995; 619627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>584205; 664041</t>
+          <t>583831; 660892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>551488; 1024127</t>
+          <t>523704; 602100</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>443700</t>
+          <t>465664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>291013</t>
+          <t>310671</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>734712</t>
+          <t>776336</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>467812; 529586</t>
+          <t>473407; 532877</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>483927; 547822</t>
+          <t>481333; 542961</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517903; 573885</t>
+          <t>516538; 576387</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>405339; 474518</t>
+          <t>429425; 497530</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>263197; 317338</t>
+          <t>259613; 318185</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>290229; 349179</t>
+          <t>291145; 350064</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>357643; 421418</t>
+          <t>354654; 420314</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>231709; 325525</t>
+          <t>284627; 338332</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>746416; 828180</t>
+          <t>741604; 829844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>792309; 883426</t>
+          <t>789262; 878328</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>886777; 975058</t>
+          <t>891023; 980218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>646212; 785210</t>
+          <t>730562; 820642</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1711533; 1832417</t>
+          <t>1720474; 1832180</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1778373; 1900727</t>
+          <t>1775043; 1894175</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1819409; 1934282</t>
+          <t>1819001; 1933753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1200308; 1723251</t>
+          <t>1614562; 1751951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>776264; 875351</t>
+          <t>771836; 872284</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>846842; 949519</t>
+          <t>846100; 953775</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1016079; 1129875</t>
+          <t>1017218; 1127265</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>850746; 1518369</t>
+          <t>859504; 958057</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2521776; 2683702</t>
+          <t>2512024; 2675544</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2647611; 2819507</t>
+          <t>2645986; 2819861</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2873027; 3037583</t>
+          <t>2865621; 3032254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2351846; 3000156</t>
+          <t>2494475; 2670491</t>
         </is>
       </c>
     </row>
